--- a/E/SWADPR.xlsx
+++ b/E/SWADPR.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20140810</t>
-  </si>
-  <si>
-    <t>G/DAY PC BB.MONSTER</t>
+    <t>20141887</t>
+  </si>
+  <si>
+    <t>GOOD DAY STANDE CARD</t>
   </si>
   <si>
     <t>SWADPR</t>
@@ -28,7 +28,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT</t>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -425,10 +425,10 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/E/SWADPR.xlsx
+++ b/E/SWADPR.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20141887</t>
-  </si>
-  <si>
-    <t>GOOD DAY STANDE CARD</t>
+    <t>20140912</t>
+  </si>
+  <si>
+    <t>SM TOLAK ANGIN 15ML</t>
   </si>
   <si>
     <t>SWADPR</t>
@@ -28,7 +28,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
+    <t>RT,(E-2B)</t>
   </si>
 </sst>
 </file>
@@ -425,7 +425,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
